--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488193_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488193_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.3579</v>
+        <v>3.8246</v>
       </c>
       <c r="E2" t="n">
-        <v>2.6558</v>
+        <v>2.8516</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7020999999999999</v>
+        <v>0.9729</v>
       </c>
       <c r="G2" t="n">
         <v>1.7978</v>
@@ -610,13 +610,13 @@
         <v>0.1853</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.4512</v>
+        <v>0.0155</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.383</v>
+        <v>-0.1871</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.0682</v>
+        <v>0.2027</v>
       </c>
       <c r="V2" t="n">
         <v>1.8259</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.9593</v>
+        <v>3.2279</v>
       </c>
       <c r="E3" t="n">
-        <v>2.2482</v>
+        <v>2.6399</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7111</v>
+        <v>0.588</v>
       </c>
       <c r="G3" t="n">
         <v>1.405</v>
@@ -688,13 +688,13 @@
         <v>2.0382</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.3519</v>
+        <v>-0.0833</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.909</v>
+        <v>-0.5173</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5571</v>
+        <v>0.434</v>
       </c>
       <c r="V3" t="n">
         <v>2.8327</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3529</v>
+        <v>-0.1072</v>
       </c>
       <c r="E6" t="n">
-        <v>1.977</v>
+        <v>1.64</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.624</v>
+        <v>-1.7472</v>
       </c>
       <c r="G6" t="n">
         <v>-1.7233</v>
@@ -922,13 +922,13 @@
         <v>1.4823</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2126</v>
+        <v>-0.2475</v>
       </c>
       <c r="T6" t="n">
-        <v>0.2661</v>
+        <v>-0.0709</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0535</v>
+        <v>-0.1766</v>
       </c>
       <c r="V6" t="n">
         <v>0.5665</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>F. NDIAYE</t>
+          <t>T. GARRETT</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.6255</v>
+        <v>-1.7841</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.4126</v>
+        <v>-1.637</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.2129</v>
+        <v>-0.1471</v>
       </c>
       <c r="G7" t="n">
-        <v>0.3907</v>
+        <v>-1.5662</v>
       </c>
       <c r="H7" t="n">
-        <v>2.4565</v>
+        <v>-0.9088000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>-2.0658</v>
+        <v>-0.6574</v>
       </c>
       <c r="J7" t="n">
-        <v>2.1908</v>
+        <v>-1.2213</v>
       </c>
       <c r="K7" t="n">
-        <v>2.6363</v>
+        <v>-1.2628</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.4455</v>
+        <v>0.0415</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.8001</v>
+        <v>-0.3448</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.1798</v>
+        <v>0.354</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.6203</v>
+        <v>-0.6989</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.1117</v>
+        <v>0.1853</v>
       </c>
       <c r="Q7" t="n">
-        <v>-3.1499</v>
+        <v>-0.1853</v>
       </c>
       <c r="R7" t="n">
-        <v>2.0382</v>
+        <v>0.3706</v>
       </c>
       <c r="S7" t="n">
-        <v>0.3549</v>
+        <v>-0.4032</v>
       </c>
       <c r="T7" t="n">
-        <v>0.2326</v>
+        <v>-0.2304</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1223</v>
+        <v>-0.1729</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.2594</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0.3139</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.5733</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>T. GARRETT</t>
+          <t>F. NDIAYE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.0352</v>
+        <v>-2.287</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.7896</v>
+        <v>-1.0002</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.2456</v>
+        <v>-1.2868</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.5662</v>
+        <v>0.3907</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.9088000000000001</v>
+        <v>2.4565</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.6574</v>
+        <v>-2.0658</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.2213</v>
+        <v>2.1908</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.2628</v>
+        <v>2.6363</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0415</v>
+        <v>-0.4455</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.3448</v>
+        <v>-1.8001</v>
       </c>
       <c r="N8" t="n">
-        <v>0.354</v>
+        <v>-0.1798</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.6989</v>
+        <v>-1.6203</v>
       </c>
       <c r="P8" t="n">
-        <v>0.1853</v>
+        <v>-1.1117</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.1853</v>
+        <v>-3.1499</v>
       </c>
       <c r="R8" t="n">
-        <v>0.3706</v>
+        <v>2.0382</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.6543</v>
+        <v>-0.3065</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.383</v>
+        <v>-0.355</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2713</v>
+        <v>0.0485</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-1.2594</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.3139</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-1.5733</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. MALICK</t>
+          <t>J. FERNANDEZ HERNANDEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.6584</v>
+        <v>-2.5714</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.5899</v>
+        <v>0.1975</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.0685</v>
+        <v>-2.769</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.1866</v>
+        <v>-2.6397</v>
       </c>
       <c r="H9" t="n">
-        <v>2.2557</v>
+        <v>1.2541</v>
       </c>
       <c r="I9" t="n">
-        <v>-4.4423</v>
+        <v>-3.8938</v>
       </c>
       <c r="J9" t="n">
-        <v>1.6704</v>
+        <v>0.5415</v>
       </c>
       <c r="K9" t="n">
-        <v>3.5555</v>
+        <v>2.9456</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.8851</v>
+        <v>-2.4041</v>
       </c>
       <c r="M9" t="n">
-        <v>-3.8571</v>
+        <v>-3.1812</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.2998</v>
+        <v>-1.6915</v>
       </c>
       <c r="O9" t="n">
-        <v>-2.5573</v>
+        <v>-1.4897</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.8529</v>
+        <v>-0.1853</v>
       </c>
       <c r="Q9" t="n">
-        <v>-4.0763</v>
+        <v>-2.2234</v>
       </c>
       <c r="R9" t="n">
-        <v>2.2234</v>
+        <v>2.0382</v>
       </c>
       <c r="S9" t="n">
-        <v>0.8139999999999999</v>
+        <v>-0.3759</v>
       </c>
       <c r="T9" t="n">
-        <v>0.5571</v>
+        <v>-0.6382</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2569</v>
+        <v>0.2624</v>
       </c>
       <c r="V9" t="n">
-        <v>0.5671</v>
+        <v>0.6294</v>
       </c>
       <c r="W9" t="n">
-        <v>1.2589</v>
+        <v>2.5177</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.6918</v>
+        <v>-1.8883</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. FERNANDEZ HERNANDEZ</t>
+          <t>B. CATALDO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.2635</v>
+        <v>-3.3864</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.3468</v>
+        <v>-1.9057</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.9167</v>
+        <v>-1.4807</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.6397</v>
+        <v>-2.2597</v>
       </c>
       <c r="H10" t="n">
-        <v>1.2541</v>
+        <v>-1.3597</v>
       </c>
       <c r="I10" t="n">
-        <v>-3.8938</v>
+        <v>-0.9001</v>
       </c>
       <c r="J10" t="n">
-        <v>0.5415</v>
+        <v>-0.7806</v>
       </c>
       <c r="K10" t="n">
-        <v>2.9456</v>
+        <v>-0.8635</v>
       </c>
       <c r="L10" t="n">
-        <v>-2.4041</v>
+        <v>0.0829</v>
       </c>
       <c r="M10" t="n">
-        <v>-3.1812</v>
+        <v>-1.4791</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.6915</v>
+        <v>-0.4961</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.4897</v>
+        <v>-0.983</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.1853</v>
+        <v>-0.3706</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.2234</v>
+        <v>-0.9264</v>
       </c>
       <c r="R10" t="n">
-        <v>2.0382</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.0679</v>
+        <v>-0.0644</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.1826</v>
+        <v>-0.1986</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1146</v>
+        <v>0.1343</v>
       </c>
       <c r="V10" t="n">
-        <v>0.6294</v>
+        <v>-0.6918</v>
       </c>
       <c r="W10" t="n">
-        <v>2.5177</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.8883</v>
+        <v>-0.6918</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>B. CATALDO</t>
+          <t>M. MALICK</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,64 +1267,64 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.6364</v>
+        <v>-3.4364</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.2542</v>
+        <v>-1.3186</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.3822</v>
+        <v>-2.1178</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.2597</v>
+        <v>-2.1866</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.3597</v>
+        <v>2.2557</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.9001</v>
+        <v>-4.4423</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.7806</v>
+        <v>1.6704</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.8635</v>
+        <v>3.5555</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0829</v>
+        <v>-1.8851</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.4791</v>
+        <v>-3.8571</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.4961</v>
+        <v>-1.2998</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.983</v>
+        <v>-2.5573</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.3706</v>
+        <v>-1.8529</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.9264</v>
+        <v>-4.0763</v>
       </c>
       <c r="R11" t="n">
-        <v>0.5558999999999999</v>
+        <v>2.2234</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3144</v>
+        <v>0.0361</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.5471</v>
+        <v>-0.1716</v>
       </c>
       <c r="U11" t="n">
-        <v>0.2328</v>
+        <v>0.2076</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.6918</v>
+        <v>0.5671</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.2589</v>
       </c>
       <c r="X11" t="n">
         <v>-0.6918</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.8077</v>
+        <v>-3.5632</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.0449</v>
+        <v>-1.7511</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.7628</v>
+        <v>-1.8121</v>
       </c>
       <c r="G12" t="n">
         <v>-1.3741</v>
@@ -1390,13 +1390,13 @@
         <v>1.1117</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.5004</v>
+        <v>-0.2559</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.909</v>
+        <v>-0.6152</v>
       </c>
       <c r="U12" t="n">
-        <v>0.4086</v>
+        <v>0.3594</v>
       </c>
       <c r="V12" t="n">
         <v>-1.0068</v>
@@ -1423,16 +1423,16 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-8.7683</v>
+        <v>-8.494899999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>1.0313</v>
+        <v>1.304700000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>-9.7995</v>
+        <v>-9.799799999999999</v>
       </c>
       <c r="G13" t="n">
-        <v>-6.5678</v>
+        <v>-6.567800000000001</v>
       </c>
       <c r="H13" t="n">
         <v>6.2964</v>
@@ -1468,13 +1468,13 @@
         <v>12.0438</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.9586</v>
+        <v>-1.6851</v>
       </c>
       <c r="T13" t="n">
-        <v>-3.2579</v>
+        <v>-2.9843</v>
       </c>
       <c r="U13" t="n">
-        <v>1.2993</v>
+        <v>1.2994</v>
       </c>
       <c r="V13" t="n">
         <v>3.4636</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>7.0976</v>
+        <v>7.5936</v>
       </c>
       <c r="E14" t="n">
-        <v>6.1896</v>
+        <v>6.8751</v>
       </c>
       <c r="F14" t="n">
-        <v>0.908</v>
+        <v>0.7185</v>
       </c>
       <c r="G14" t="n">
         <v>7.3667</v>
@@ -1546,13 +1546,13 @@
         <v>2.9646</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.1214</v>
+        <v>0.3746</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.2373</v>
+        <v>-0.5518</v>
       </c>
       <c r="U14" t="n">
-        <v>1.1159</v>
+        <v>0.9264</v>
       </c>
       <c r="V14" t="n">
         <v>-1.2594</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.5639</v>
+        <v>3.0868</v>
       </c>
       <c r="E15" t="n">
-        <v>5.7539</v>
+        <v>6.0477</v>
       </c>
       <c r="F15" t="n">
-        <v>-3.19</v>
+        <v>-2.9609</v>
       </c>
       <c r="G15" t="n">
         <v>0.8234</v>
@@ -1624,13 +1624,13 @@
         <v>1.4823</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.0562</v>
+        <v>0.4666</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.0161</v>
+        <v>0.2776</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0401</v>
+        <v>0.189</v>
       </c>
       <c r="V15" t="n">
         <v>0.3144</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>G. MAIGA</t>
+          <t>F. GONZALEZ ROSCO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.0567</v>
+        <v>2.2172</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.07829999999999999</v>
+        <v>0.8908</v>
       </c>
       <c r="F16" t="n">
-        <v>2.135</v>
+        <v>1.3264</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.2938</v>
+        <v>1.3857</v>
       </c>
       <c r="H16" t="n">
-        <v>-3.2771</v>
+        <v>0.8925</v>
       </c>
       <c r="I16" t="n">
-        <v>1.9832</v>
+        <v>0.4931</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.009599999999999999</v>
+        <v>1.1765</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.5855</v>
+        <v>1.0521</v>
       </c>
       <c r="L16" t="n">
-        <v>1.5759</v>
+        <v>0.1244</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.2842</v>
+        <v>0.2092</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.6915</v>
+        <v>-0.1596</v>
       </c>
       <c r="O16" t="n">
-        <v>0.4073</v>
+        <v>0.3687</v>
       </c>
       <c r="P16" t="n">
-        <v>0.5558999999999999</v>
+        <v>1.1117</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.8529</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2.4087</v>
+        <v>1.1117</v>
       </c>
       <c r="S16" t="n">
-        <v>2.1658</v>
+        <v>0.0348</v>
       </c>
       <c r="T16" t="n">
-        <v>1.1553</v>
+        <v>0.0299</v>
       </c>
       <c r="U16" t="n">
-        <v>1.0105</v>
+        <v>0.005</v>
       </c>
       <c r="V16" t="n">
-        <v>0.6289</v>
+        <v>-0.315</v>
       </c>
       <c r="W16" t="n">
-        <v>0.6289</v>
+        <v>-0.3155</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>0.0005</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.9168</v>
+        <v>2.0399</v>
       </c>
       <c r="E17" t="n">
         <v>1.814</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1028</v>
+        <v>0.2259</v>
       </c>
       <c r="G17" t="n">
         <v>2.9997</v>
@@ -1780,13 +1780,13 @@
         <v>0.5558999999999999</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.3979</v>
+        <v>-0.2748</v>
       </c>
       <c r="T17" t="n">
         <v>-0.2736</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1244</v>
+        <v>-0.0012</v>
       </c>
       <c r="V17" t="n">
         <v>-0.3144</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>F. GONZALEZ ROSCO</t>
+          <t>L. LOPEZ CALZADA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.7516</v>
+        <v>1.9172</v>
       </c>
       <c r="E18" t="n">
-        <v>0.4991</v>
+        <v>2.7426</v>
       </c>
       <c r="F18" t="n">
-        <v>1.2525</v>
+        <v>-0.8254</v>
       </c>
       <c r="G18" t="n">
-        <v>1.3857</v>
+        <v>1.3894</v>
       </c>
       <c r="H18" t="n">
-        <v>0.8925</v>
+        <v>-2.5598</v>
       </c>
       <c r="I18" t="n">
-        <v>0.4931</v>
+        <v>3.9492</v>
       </c>
       <c r="J18" t="n">
-        <v>1.1765</v>
+        <v>2.7578</v>
       </c>
       <c r="K18" t="n">
-        <v>1.0521</v>
+        <v>-0.6535</v>
       </c>
       <c r="L18" t="n">
-        <v>0.1244</v>
+        <v>3.4113</v>
       </c>
       <c r="M18" t="n">
-        <v>0.2092</v>
+        <v>-1.3684</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.1596</v>
+        <v>-1.9063</v>
       </c>
       <c r="O18" t="n">
-        <v>0.3687</v>
+        <v>0.5379</v>
       </c>
       <c r="P18" t="n">
-        <v>1.1117</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-1.8529</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1117</v>
+        <v>1.8529</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.4308</v>
+        <v>0.8421999999999999</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.3619</v>
+        <v>-0.0506</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0689</v>
+        <v>0.8928</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.315</v>
+        <v>-0.3144</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.3155</v>
+        <v>1.8883</v>
       </c>
       <c r="X18" t="n">
-        <v>0.0005</v>
+        <v>-2.2027</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>L. LOPEZ CALZADA</t>
+          <t>G. MAIGA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.4189</v>
+        <v>0.9628</v>
       </c>
       <c r="E19" t="n">
-        <v>2.4488</v>
+        <v>-1.2535</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.0298</v>
+        <v>2.2163</v>
       </c>
       <c r="G19" t="n">
-        <v>1.3894</v>
+        <v>-1.2938</v>
       </c>
       <c r="H19" t="n">
-        <v>-2.5598</v>
+        <v>-3.2771</v>
       </c>
       <c r="I19" t="n">
-        <v>3.9492</v>
+        <v>1.9832</v>
       </c>
       <c r="J19" t="n">
-        <v>2.7578</v>
+        <v>-0.009599999999999999</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.6535</v>
+        <v>-1.5855</v>
       </c>
       <c r="L19" t="n">
-        <v>3.4113</v>
+        <v>1.5759</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.3684</v>
+        <v>-1.2842</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.9063</v>
+        <v>-1.6915</v>
       </c>
       <c r="O19" t="n">
-        <v>0.5379</v>
+        <v>0.4073</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="Q19" t="n">
         <v>-1.8529</v>
       </c>
       <c r="R19" t="n">
-        <v>1.8529</v>
+        <v>2.4087</v>
       </c>
       <c r="S19" t="n">
-        <v>0.344</v>
+        <v>1.0719</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3444</v>
+        <v>-0.0199</v>
       </c>
       <c r="U19" t="n">
-        <v>0.6884</v>
+        <v>1.0918</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.3144</v>
+        <v>0.6289</v>
       </c>
       <c r="W19" t="n">
-        <v>1.8883</v>
+        <v>0.6289</v>
       </c>
       <c r="X19" t="n">
-        <v>-2.2027</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.2716</v>
+        <v>-0.4686</v>
       </c>
       <c r="E20" t="n">
         <v>-0.6837</v>
       </c>
       <c r="F20" t="n">
-        <v>0.4121</v>
+        <v>0.2152</v>
       </c>
       <c r="G20" t="n">
         <v>0.9604</v>
@@ -2014,13 +2014,13 @@
         <v>0.9264</v>
       </c>
       <c r="S20" t="n">
-        <v>0.3064</v>
+        <v>0.1094</v>
       </c>
       <c r="T20" t="n">
         <v>-0.2524</v>
       </c>
       <c r="U20" t="n">
-        <v>0.5588</v>
+        <v>0.3619</v>
       </c>
       <c r="V20" t="n">
         <v>0.3144</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.6021</v>
+        <v>-0.5775</v>
       </c>
       <c r="E21" t="n">
         <v>-0.905</v>
       </c>
       <c r="F21" t="n">
-        <v>0.3028</v>
+        <v>0.3275</v>
       </c>
       <c r="G21" t="n">
         <v>-0.7155</v>
@@ -2092,13 +2092,13 @@
         <v>0.3706</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.2572</v>
+        <v>-0.2325</v>
       </c>
       <c r="T21" t="n">
         <v>-0.2736</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0164</v>
+        <v>0.041</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.061</v>
+        <v>-2.2969</v>
       </c>
       <c r="E22" t="n">
-        <v>0.3406</v>
+        <v>-0.149</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.4016</v>
+        <v>-2.1479</v>
       </c>
       <c r="G22" t="n">
         <v>-2.2869</v>
@@ -2170,13 +2170,13 @@
         <v>0.3706</v>
       </c>
       <c r="S22" t="n">
-        <v>1.1142</v>
+        <v>0.8783</v>
       </c>
       <c r="T22" t="n">
-        <v>1.1627</v>
+        <v>0.6731</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0485</v>
+        <v>0.2052</v>
       </c>
       <c r="V22" t="n">
         <v>-1.2589</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>S. CABALLERO CARPIO</t>
+          <t>J. LOPEZ YUSTE</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.4185</v>
+        <v>-2.4143</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.3372</v>
+        <v>-3.6757</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.08119999999999999</v>
+        <v>1.2615</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.6844</v>
+        <v>-1.3768</v>
       </c>
       <c r="H23" t="n">
-        <v>-3.0054</v>
+        <v>-0.2292</v>
       </c>
       <c r="I23" t="n">
-        <v>0.3211</v>
+        <v>-1.1476</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.8112</v>
+        <v>-0.7597</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.8942</v>
+        <v>0.9488</v>
       </c>
       <c r="L23" t="n">
-        <v>0.0829</v>
+        <v>-1.7085</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.8731</v>
+        <v>-0.6171</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.1113</v>
+        <v>-1.178</v>
       </c>
       <c r="O23" t="n">
-        <v>0.2381</v>
+        <v>0.5609</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>0.9264</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.9264</v>
+        <v>-1.8529</v>
       </c>
       <c r="R23" t="n">
-        <v>0.9264</v>
+        <v>2.7793</v>
       </c>
       <c r="S23" t="n">
-        <v>0.2659</v>
+        <v>-0.7045</v>
       </c>
       <c r="T23" t="n">
-        <v>0.4004</v>
+        <v>-1.0626</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1346</v>
+        <v>0.3581</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>-1.2594</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>-0.0005</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>-1.2589</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>J. LOPEZ YUSTE</t>
+          <t>S. CABALLERO CARPIO</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.684</v>
+        <v>-2.639</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.8716</v>
+        <v>-2.5331</v>
       </c>
       <c r="F24" t="n">
-        <v>1.1876</v>
+        <v>-0.1059</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.3768</v>
+        <v>-2.6844</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.2292</v>
+        <v>-3.0054</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.1476</v>
+        <v>0.3211</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.7597</v>
+        <v>-1.8112</v>
       </c>
       <c r="K24" t="n">
-        <v>0.9488</v>
+        <v>-1.8942</v>
       </c>
       <c r="L24" t="n">
-        <v>-1.7085</v>
+        <v>0.0829</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.6171</v>
+        <v>-0.8731</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.178</v>
+        <v>-1.1113</v>
       </c>
       <c r="O24" t="n">
-        <v>0.5609</v>
+        <v>0.2381</v>
       </c>
       <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>-0.9264</v>
+      </c>
+      <c r="R24" t="n">
         <v>0.9264</v>
       </c>
-      <c r="Q24" t="n">
-        <v>-1.8529</v>
-      </c>
-      <c r="R24" t="n">
-        <v>2.7793</v>
-      </c>
       <c r="S24" t="n">
-        <v>-0.9742</v>
+        <v>0.0454</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.2584</v>
+        <v>0.2046</v>
       </c>
       <c r="U24" t="n">
-        <v>0.2842</v>
+        <v>-0.1592</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.2594</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>-0.0005</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.2589</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -2359,19 +2359,19 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>8.768300000000004</v>
+        <v>9.421199999999999</v>
       </c>
       <c r="E25" t="n">
         <v>9.170199999999998</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.4018000000000002</v>
+        <v>0.2512</v>
       </c>
       <c r="G25" t="n">
-        <v>6.567899999999997</v>
+        <v>6.567899999999998</v>
       </c>
       <c r="H25" t="n">
-        <v>-6.296499999999999</v>
+        <v>-6.2965</v>
       </c>
       <c r="I25" t="n">
         <v>12.8643</v>
@@ -2404,13 +2404,13 @@
         <v>15.7494</v>
       </c>
       <c r="S25" t="n">
-        <v>1.9586</v>
+        <v>2.6114</v>
       </c>
       <c r="T25" t="n">
         <v>-1.2993</v>
       </c>
       <c r="U25" t="n">
-        <v>3.2577</v>
+        <v>3.9108</v>
       </c>
       <c r="V25" t="n">
         <v>-3.4638</v>
